--- a/artfynd/A 6542-2025 artfynd.xlsx
+++ b/artfynd/A 6542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,148 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123803178</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8445</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sörmon, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>404433</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6582911</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Segerstad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Tallåga # Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6542-2025 artfynd.xlsx
+++ b/artfynd/A 6542-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>123803178</v>
       </c>
       <c r="B3" t="n">
-        <v>8445</v>
+        <v>8447</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
